--- a/asistencias_excel/Asistencia_Ayudantias_CIT3203_CA03_-_Sección_3_UDP.xlsx
+++ b/asistencias_excel/Asistencia_Ayudantias_CIT3203_CA03_-_Sección_3_UDP.xlsx
@@ -1752,7 +1752,7 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="str">
         <v>S/C</v>
@@ -1794,16 +1794,16 @@
         <v>0.4</v>
       </c>
       <c r="W20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X20">
         <v>4</v>
       </c>
       <c r="Y20" t="str">
-        <v>50%</v>
+        <v>75%</v>
       </c>
       <c r="Z20" t="str">
-        <v>RI</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="21">
@@ -2792,7 +2792,7 @@
         <v>11</v>
       </c>
       <c r="I33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J33" t="str">
         <v>S/C</v>
